--- a/Resolved_Errors_Log.xlsx
+++ b/Resolved_Errors_Log.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resolved Issues &amp; Fixes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,19 +27,19 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="004A5568"/>
+      <color rgb="FF4A5568"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -51,24 +50,30 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001A365D"/>
+      <color rgb="FF1A365D"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001A202C"/>
+      <color rgb="FF1A202C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="002D3748"/>
+      <color rgb="FF2D3748"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00137333"/>
+      <color rgb="FF137333"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1B5E20"/>
       <sz val="11"/>
     </font>
     <font>
@@ -76,7 +81,7 @@
       <color rgb="001B5E20"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -85,26 +90,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D3B49"/>
-        <bgColor rgb="000D3B49"/>
+        <fgColor rgb="FF0D3B49"/>
+        <bgColor rgb="FF0D3B49"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A535C"/>
-        <bgColor rgb="001A535C"/>
+        <fgColor rgb="FF1A535C"/>
+        <bgColor rgb="FF1A535C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
+        <fgColor rgb="FFE6F4EA"/>
+        <bgColor rgb="FFE6F4EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -123,17 +133,33 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="FFCBD5E0"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="FFCBD5E0"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="FFCBD5E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="FFCBD5E0"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -153,14 +179,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -197,9 +217,22 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -562,748 +595,927 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" style="14" min="1" max="1"/>
+    <col width="36" customWidth="1" style="14" min="2" max="2"/>
+    <col width="42" customWidth="1" style="14" min="3" max="3"/>
+    <col width="55" customWidth="1" style="14" min="4" max="5"/>
+    <col width="12" customWidth="1" style="14" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="14">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Ride Round Up - System Issues, Bugs &amp; Resolution Log</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="24" customHeight="1" s="14">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Complete non-technical tracking of every bug, data safety issue, and workflow friction resolved to date.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="28.05" customHeight="1" s="14">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>S.No</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Module / Area</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Error / Issue Name</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Error Description (What Was Happening)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Solution (How It Was Solved)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5" ht="48" customHeight="1" s="14">
+      <c r="A5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Database Protection</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Automated Tests Wiping Database Records</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Whenever automated tests were executed, they were accidentally connecting to the actual live working database and deleting all cars, models, and brands to start fresh tests.</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Created an unbreakable security guard that blocks all automated tests from ever touching the main database. Tests now strictly run only in isolated, harmless sandbox environments with zero risk to real data.</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="9" t="n">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60.6" customHeight="1" s="14">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Car Creation Wizard (Steps 3, 4, 5)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>System Slowdown &amp; Network Flooding (20+ Calls Per Car)</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>When picking features, colors, or markets for a car, clicking an option sent an immediate separate message to the server for every single click. Picking 10 items fired 20+ separate network requests, making the page laggy and causing save conflicts.</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Changed the whole workflow into a fast 'Batch Save'. Now you can freely select or customize as many features, colors, and markets as you want with zero lag. The system packages everything together and saves it cleanly in one single click when you press 'Save &amp; Next'.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="82.2" customHeight="1" s="14">
+      <c r="A7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Specifications Step (Step 2)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Contradictory 'Not Found' AND 'Already Exists' Error</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>When editing specifications for an existing car, the screen showed two opposite error banners at the exact same time: 'Specification not found' and 'Specification already exists'. You were blocked from editing or saving.</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>The server was hiding specifications whose status flag was turned off, while the database still knew the car already had specifications. We updated the system so it always finds the car's specifications regardless of status, restored missing status flags, and removed the duplicate block.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="9" t="n">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62.4" customHeight="1" s="14">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Colors Management</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Strict Manufacturer Code &amp; Duplicate Color Block</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>The color setup page forced users to enter a manufacturer code even when one wasn't available, didn't enforce the paint finish (e.g. Matte, Metallic), and stopped users from adding the same color in different finishes (e.g. Matte Black vs Glossy Black).</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Made the manufacturer code optional so you are never stuck. Made the finish type mandatory (Solid, Metallic, Matte, Pearlescent), and updated the rules so the same color can now be freely created in different finishes without false duplicate errors.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="14">
+      <c r="A9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Vehicle Basic Info (Step 1)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Model Dropdown Showing 'No options' for Certain Brands</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>When selecting brands like Bentley or Bugatti, the Model dropdown showed 'No options' with no explanation, making it look like a model was lost or the system was broken.</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Identified that Bentley and Bugatti currently had 0 models created in the database. Added a clear, helpful message: 'No models for this brand yet. Click + to add one.' so users know exactly what to do.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="9" t="n">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="14">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>All List Pages (Models, Generations, Cars)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Filter Dropdown Page Crashes</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>On the Models, Generations, and Cars pages, if you set a filter back to 'All Brands' or 'All Models', the page could crash with a white screen error ('Cannot read properties of undefined').</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Added safe backup handling for all filter lists. Even if a brand has no models or the filter is cleared, the system gracefully handles the list without ever crashing.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="14">
+      <c r="A11" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Vehicle Wizard &amp; Markets</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Missing Options Due to Hardcoded 100-Item Limit</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>The dropdowns for Brands, Models, and Markets were only asking the database for the first 100 records. Once you had more than 100 items, any item past #100 was completely invisible in the list.</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Increased the limit to 1,000 items across all dropdowns. Now every brand, model, generation, and market is fully visible and selectable.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="9" t="n">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="57" customHeight="1" s="14">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Quick-Add Popups (+ Button)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Blank Input Flash After Adding a Brand/Model</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>When clicking the '+' button to quickly add a brand or model inside the vehicle creator, the popup would close but the dropdown input would stay blank or show 'No options' for a few moments while reloading from the internet.</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Upgraded the quick-add system to immediately place the newly created brand or model directly into the dropdown with zero wait time and zero screen flickering.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="14">
+      <c r="A13" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Reviews Dashboard</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Review Total Badge Showing Only 10 Reviews</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>The top of the Reviews page showed a badge like '10 total', even when there were dozens of reviews in the database, because it was only counting the current page of 10 items.</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Fixed the counter to read the true total count directly from the server. The badge now accurately displays the exact total number of reviews across all pages.</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="9" t="n">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="14">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Articles Management</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Articles List Missing a Search Bar</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Unlike Brands, Cars, and Models which had search bars, the Articles page had no search box, forcing users to click through pages one by one to find an article.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Added an instant search bar with a magnifying glass icon to the Articles page, matching the rest of the dashboard.</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="14">
+      <c r="A15" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Vehicle Basic Info (Step 1)</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Generation Field Jumping and Displacing the Form</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>When a model had no generations created, the input box suddenly vanished and was replaced by a blue notification banner, breaking the 3-column layout and making the page jump.</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Kept the field as a steady, consistent input box with clear helper text ('No generations for this model — leave blank or click +'). The layout now stays cleanly aligned in all situations.</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="9" t="n">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="14">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Media Uploads (Step 6)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Inconsistent Browser Popups on Photo Deletion</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>When deleting a car image, the browser popped up an old-fashioned native gray prompt box ('Are you sure you want to delete?'), which didn't match the modern design of the rest of the website.</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Replaced the browser popup with a clean, branded confirmation dialog modal matching the rest of the dashboard.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="14">
+      <c r="A17" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Car Creation Dropdown</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Draft Models Indistinguishable From Published Models</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Models that were still unpublished drafts looked identical in the dropdown to live models, making it easy to select the wrong model accidentally.</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Added a clear '(Draft)' tag next to any draft model in the dropdown list so you instantly know which models are still in progress.</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="n">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="72" customHeight="1" s="14">
+      <c r="A18" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Vehicle Edit (Basic Info)</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Brand Dropdown Blank When Vehicle Has No Generation</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>When editing a car that had a Brand and Model but no Generation selected, the Brand box appeared empty and the Model dropdown was locked. It looked like the data was lost, even though it was still saved in the database. About 27 vehicles were affected.</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>The system now always loads Brand and Model directly from the car record, even when Generation is blank. Editing these cars shows Brand and Model correctly again. No data was deleted or changed.</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="n">
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="72" customHeight="1" s="14">
+      <c r="A19" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>All Dropdowns (Brands, Models, Features, Colors, Markets)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Hidden Items Past the First 100 / 200 Records</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Dropdown lists and the Features step were silently cutting off after 100 or 200 items. The screen asked for up to 1,000, but the server ignored anything above 100. With 205 features in the system, the last 5 features never appeared when assigning them to a car.</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Raised the server limit to 1,000 and raised the Features/Colors/Markets requests to match. Every active feature, color, brand, model, and market can now appear in the wizard.</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="n">
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="57.6" customHeight="1" s="14">
+      <c r="A20" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Specifications Step (Step 2) &amp; Review</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Fuel Economy Saved But Invisible</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Fuel economy numbers (city, highway, combined, unit) were being stored in the database for dozens of cars, but there was no place on the Specifications form or Review/Detail screens to see or edit them. Staff thought the data was missing.</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Added a Fuel Economy section on the Specifications step and showed the same values on Review and Vehicle Detail. Existing saved numbers now display without any data rebuild.</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="n">
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="64.8" customHeight="1" s="14">
+      <c r="A21" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Features Step (Step 3) &amp; Quick Add</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Feature Save Failed With "Expected String, Received Object"</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>After selecting many features and pressing Save, the system rejected the save saying Feature ID was the wrong type. Existing features came back from the server as full objects (with name, category, etc.) instead of a simple ID text.</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>When saving, the system now always sends only the plain Feature ID text. Bulk save continues to work in one request. Existing mappings were not wiped.</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="n">
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="57.6" customHeight="1" s="14">
+      <c r="A22" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Quick Add Popups on Edit Vehicle</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>"Feature Not Found" When Trying to Add a New Feature</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>On the Edit Vehicle page, clicking Add New Feature opened a form titled Edit Feature and showed Feature not found twice. The popup was accidentally treating the car ID from the web address as a feature ID.</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Quick-add popups for Feature, Color, Brand, Model, and Generation now always create new items and ignore the car ID in the address bar.</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="n">
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="72" customHeight="1" s="14">
+      <c r="A23" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Features Master List / Search</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Duplicate Name Error But Search Found Nothing</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Trying to create "Power Adjustable Seats" said it already exists, but searching that exact phrase on the Features page found nothing. The real item was named "Power-Adjustable Front Seats (14-Way)" (with a hyphen) and shared the same internal short code.</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Search now treats spaces and hyphens the same, so either phrase finds the existing feature. The duplicate error also shows the exact existing name so staff know which one to use.</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="n">
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="43.2" customHeight="1" s="14">
+      <c r="A24" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Media Step (Step 6)</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Uploading Several Photos Marked All of Them as Primary</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>When uploading multiple photos at once to an empty gallery, every photo could be marked as the cover/primary image at the same time because of a race between parallel uploads.</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Only the first photo in a multi-upload is marked primary when the gallery was empty. Setting a new primary also uses a single update (the server clears the old primary automatically).</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="n">
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="43.2" customHeight="1" s="14">
+      <c r="A25" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Pricing &amp; Markets Step (Step 5)</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>In-Progress Market Edits Getting Wiped Mid-Form</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>While editing prices or availability for markets, a background data refresh could reset the form and erase unsaved typing before Save &amp; Continue.</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Unsaved market edits are now kept until you successfully save. After a successful save, the form reloads cleanly from the server.</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="n">
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="43.2" customHeight="1" s="14">
+      <c r="A26" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Cars List &amp; Vehicle Detail</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Generation Shown as "Unknown" and Brand/Model Missing</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>On the Cars list, vehicles without a generation showed "Unknown". The Vehicle Detail page did not show Brand or Model at all, so staff could not confirm hierarchy after saving.</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>List now shows a dash when generation is empty, and shows the Model name in a new column. Detail and Review screens now show Brand, Model, and Generation clearly.</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Solved</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="n">
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="43.2" customHeight="1" s="14">
+      <c r="A27" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Review Step (Step 7)</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>Optional Features Labeled "Not Applicable"</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>On the final Review screen, features marked Optional were incorrectly labeled "Not Applicable", which confused reviewers about what the car actually offers.</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Review now shows the real availability word (Standard / Optional / Unavailable). ADAS and fuel economy also appear on Review.</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Specifications Step (Step 2)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Page Crash After Adding Fuel Economy Section</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>After Fuel Economy fields were added, the Specifications step crashed with a red Vite error about mismatched Box/Stack tags, so the form could not open at all.</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>Removed an accidental extra closing tag that broke the page layout. The Specifications step opens and saves again, including Fuel Economy.</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard Production Build (Render)</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Deploy Build Failed on Type Errors</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>The dashboard could not be built for Render because TypeScript complained that Brand/Model/Generation and ADAS fields were missing from the vehicle and safety types, even though the API already returned them.</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>Updated the vehicle and safety type definitions and added safe display helpers. Production build (npm run build) now completes successfully.</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Login / Session</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Session Expired Immediately Instead of Refreshing</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>When the short-lived access token expired, the dashboard tried to refresh the session with an empty request. The server requires the refresh token, so users were kicked to Login even during active work.</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>Login now stores the refresh token, and the refresh call sends it correctly. Sessions renew quietly when the access token expires.</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Pricing &amp; Markets Step (Step 5)</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Clearing a Price Did Not Stick</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>If a market price was set and later cleared to zero, the old price came back after save because the system only sent prices above zero and never told the database to remove the old value.</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>Clearing the price now sends zero and the server removes the stored price. Cleared prices stay cleared after reload.</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Reviews Page</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Review Pagination Total Dropped by API Client</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>The reviews request was dropping the total-count metadata from the server response, which could make pagination look incomplete.</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>The reviews API client now keeps both the list and the true total count from the server.</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Render Deployment (Dashboard SPA)</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Refreshing Edit Vehicle Page Gave 404 on Hosting</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>On static hosting like Render, refreshing a deep link such as /cars/123/edit can show Not Found because the host looks for a real folder instead of the React app.</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Added SPA rewrite files (_redirects and static.json) so deep links load the app correctly after refresh. Added .env.example reminding that VITE_API_URL must be set for production builds.</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>Solved</t>
         </is>
